--- a/artfynd/A 31957-2025 artfynd.xlsx
+++ b/artfynd/A 31957-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -922,7 +922,7 @@
         <v>126844799</v>
       </c>
       <c r="B4" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>126844768</v>
       </c>
       <c r="B5" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1155,53 +1155,57 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126844792</v>
+        <v>126844817</v>
       </c>
       <c r="B6" t="n">
-        <v>98361</v>
+        <v>56849</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>knärot, Lång, Dlr</t>
+          <t>Tjäderspilning, Lång, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478438</v>
+        <v>478451</v>
       </c>
       <c r="R6" t="n">
-        <v>6729346</v>
+        <v>6729364</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1246,13 +1250,17 @@
           <t>15:00</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>spillning, Sandbad</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1271,57 +1279,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126844817</v>
+        <v>126844792</v>
       </c>
       <c r="B7" t="n">
-        <v>56849</v>
+        <v>98436</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tjäderspilning, Lång, Dlr</t>
+          <t>knärot, Lång, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478451</v>
+        <v>478438</v>
       </c>
       <c r="R7" t="n">
-        <v>6729364</v>
+        <v>6729346</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1366,17 +1370,13 @@
           <t>15:00</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>spillning, Sandbad</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1392,6 +1392,520 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>127302956</v>
+      </c>
+      <c r="B8" t="n">
+        <v>56849</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>N Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>478532</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6729375</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre balningsgrop.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>127303713</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79629</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>478482</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6729414</v>
+      </c>
+      <c r="S9" t="n">
+        <v>50</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>127303688</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79629</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>478523</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6729413</v>
+      </c>
+      <c r="S10" t="n">
+        <v>50</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127303666</v>
+      </c>
+      <c r="B11" t="n">
+        <v>78678</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>353</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>478520</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6729405</v>
+      </c>
+      <c r="S11" t="n">
+        <v>50</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>127302595</v>
+      </c>
+      <c r="B12" t="n">
+        <v>78770</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>N Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>478531</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6729399</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31957-2025 artfynd.xlsx
+++ b/artfynd/A 31957-2025 artfynd.xlsx
@@ -795,57 +795,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126844749</v>
+        <v>126844799</v>
       </c>
       <c r="B3" t="n">
-        <v>56849</v>
+        <v>98442</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tjäderspilning, Lång, Dlr</t>
+          <t>knärot, Lång, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478451</v>
+        <v>478423</v>
       </c>
       <c r="R3" t="n">
-        <v>6729443</v>
+        <v>6729337</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,17 +886,13 @@
           <t>15:00</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>spillning</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -919,53 +911,57 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126844799</v>
+        <v>126844749</v>
       </c>
       <c r="B4" t="n">
-        <v>98436</v>
+        <v>56849</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>knärot, Lång, Dlr</t>
+          <t>Tjäderspilning, Lång, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478423</v>
+        <v>478451</v>
       </c>
       <c r="R4" t="n">
-        <v>6729337</v>
+        <v>6729443</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,13 +1006,17 @@
           <t>15:00</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>spillning</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1038,7 +1038,7 @@
         <v>126844768</v>
       </c>
       <c r="B5" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
         <v>126844792</v>
       </c>
       <c r="B7" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1395,56 +1395,51 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127302956</v>
+        <v>127303713</v>
       </c>
       <c r="B8" t="n">
-        <v>56849</v>
+        <v>79632</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478532</v>
+        <v>478482</v>
       </c>
       <c r="R8" t="n">
-        <v>6729375</v>
+        <v>6729414</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1476,80 +1471,81 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Äldre balningsgrop.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127303713</v>
+        <v>127302956</v>
       </c>
       <c r="B9" t="n">
-        <v>79629</v>
+        <v>56849</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478482</v>
+        <v>478532</v>
       </c>
       <c r="R9" t="n">
-        <v>6729414</v>
+        <v>6729375</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1581,25 +1577,29 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre balningsgrop.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1609,7 +1609,7 @@
         <v>127303688</v>
       </c>
       <c r="B10" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>127303666</v>
       </c>
       <c r="B11" t="n">
-        <v>78678</v>
+        <v>78681</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>127302595</v>
       </c>
       <c r="B12" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 31957-2025 artfynd.xlsx
+++ b/artfynd/A 31957-2025 artfynd.xlsx
@@ -795,53 +795,57 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126844799</v>
+        <v>126844749</v>
       </c>
       <c r="B3" t="n">
-        <v>98442</v>
+        <v>56849</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>knärot, Lång, Dlr</t>
+          <t>Tjäderspilning, Lång, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478423</v>
+        <v>478451</v>
       </c>
       <c r="R3" t="n">
-        <v>6729337</v>
+        <v>6729443</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -886,13 +890,17 @@
           <t>15:00</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>spillning</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -911,57 +919,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126844749</v>
+        <v>126844799</v>
       </c>
       <c r="B4" t="n">
-        <v>56849</v>
+        <v>98442</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tjäderspilning, Lång, Dlr</t>
+          <t>knärot, Lång, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478451</v>
+        <v>478423</v>
       </c>
       <c r="R4" t="n">
-        <v>6729443</v>
+        <v>6729337</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1006,17 +1010,13 @@
           <t>15:00</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>spillning</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1395,51 +1395,56 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127303713</v>
+        <v>127302956</v>
       </c>
       <c r="B8" t="n">
-        <v>79632</v>
+        <v>56849</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478482</v>
+        <v>478532</v>
       </c>
       <c r="R8" t="n">
-        <v>6729414</v>
+        <v>6729375</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1471,81 +1476,80 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre balningsgrop.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127302956</v>
+        <v>127303713</v>
       </c>
       <c r="B9" t="n">
-        <v>56849</v>
+        <v>79632</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478532</v>
+        <v>478482</v>
       </c>
       <c r="R9" t="n">
-        <v>6729375</v>
+        <v>6729414</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1577,29 +1581,25 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre balningsgrop.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1707,10 +1707,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127303666</v>
+        <v>127302595</v>
       </c>
       <c r="B11" t="n">
-        <v>78681</v>
+        <v>78773</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1718,21 +1718,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1741,17 +1741,17 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478520</v>
+        <v>478531</v>
       </c>
       <c r="R11" t="n">
-        <v>6729405</v>
+        <v>6729399</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1796,22 +1796,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127302595</v>
+        <v>127303666</v>
       </c>
       <c r="B12" t="n">
-        <v>78773</v>
+        <v>78681</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1819,21 +1819,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1842,17 +1842,17 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478531</v>
+        <v>478520</v>
       </c>
       <c r="R12" t="n">
-        <v>6729399</v>
+        <v>6729405</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1897,12 +1897,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 31957-2025 artfynd.xlsx
+++ b/artfynd/A 31957-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1707,10 +1707,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127302595</v>
+        <v>127303666</v>
       </c>
       <c r="B11" t="n">
-        <v>78773</v>
+        <v>78681</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1718,21 +1718,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1741,17 +1741,17 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478531</v>
+        <v>478520</v>
       </c>
       <c r="R11" t="n">
-        <v>6729399</v>
+        <v>6729405</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1796,22 +1796,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127303666</v>
+        <v>127302595</v>
       </c>
       <c r="B12" t="n">
-        <v>78681</v>
+        <v>78773</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1819,21 +1819,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1842,17 +1842,17 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478520</v>
+        <v>478531</v>
       </c>
       <c r="R12" t="n">
-        <v>6729405</v>
+        <v>6729399</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1897,15 +1897,595 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127302603</v>
+      </c>
+      <c r="B13" t="n">
+        <v>56849</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>478336</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6729407</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>127302681</v>
+      </c>
+      <c r="B14" t="n">
+        <v>56849</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>478358</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6729449</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>på liten sten</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127302695</v>
+      </c>
+      <c r="B15" t="n">
+        <v>56849</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>478360</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6729494</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>127303954</v>
+      </c>
+      <c r="B16" t="n">
+        <v>56849</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>478281</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6729282</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127303837</v>
+      </c>
+      <c r="B17" t="n">
+        <v>56849</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>478296</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6729357</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31957-2025 artfynd.xlsx
+++ b/artfynd/A 31957-2025 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>126844799</v>
       </c>
       <c r="B4" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>126844768</v>
       </c>
       <c r="B5" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1155,57 +1155,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126844817</v>
+        <v>126844792</v>
       </c>
       <c r="B6" t="n">
-        <v>56849</v>
+        <v>98443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tjäderspilning, Lång, Dlr</t>
+          <t>knärot, Lång, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478451</v>
+        <v>478438</v>
       </c>
       <c r="R6" t="n">
-        <v>6729364</v>
+        <v>6729346</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1250,17 +1246,13 @@
           <t>15:00</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>spillning, Sandbad</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1279,53 +1271,57 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126844792</v>
+        <v>126844817</v>
       </c>
       <c r="B7" t="n">
-        <v>98442</v>
+        <v>56849</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>knärot, Lång, Dlr</t>
+          <t>Tjäderspilning, Lång, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478438</v>
+        <v>478451</v>
       </c>
       <c r="R7" t="n">
-        <v>6729346</v>
+        <v>6729364</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1370,13 +1366,17 @@
           <t>15:00</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>spillning, Sandbad</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1395,56 +1395,51 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127302956</v>
+        <v>127303713</v>
       </c>
       <c r="B8" t="n">
-        <v>56849</v>
+        <v>79632</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478532</v>
+        <v>478482</v>
       </c>
       <c r="R8" t="n">
-        <v>6729375</v>
+        <v>6729414</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1476,80 +1471,81 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Äldre balningsgrop.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127303713</v>
+        <v>127302956</v>
       </c>
       <c r="B9" t="n">
-        <v>79632</v>
+        <v>56849</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478482</v>
+        <v>478532</v>
       </c>
       <c r="R9" t="n">
-        <v>6729414</v>
+        <v>6729375</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1581,25 +1577,29 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre balningsgrop.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1707,10 +1707,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127303666</v>
+        <v>127302595</v>
       </c>
       <c r="B11" t="n">
-        <v>78681</v>
+        <v>78773</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1718,21 +1718,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1741,17 +1741,17 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478520</v>
+        <v>478531</v>
       </c>
       <c r="R11" t="n">
-        <v>6729405</v>
+        <v>6729399</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1796,22 +1796,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127302595</v>
+        <v>127303666</v>
       </c>
       <c r="B12" t="n">
-        <v>78773</v>
+        <v>78681</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1819,21 +1819,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1842,17 +1842,17 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478531</v>
+        <v>478520</v>
       </c>
       <c r="R12" t="n">
-        <v>6729399</v>
+        <v>6729405</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1897,12 +1897,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 31957-2025 artfynd.xlsx
+++ b/artfynd/A 31957-2025 artfynd.xlsx
@@ -1155,53 +1155,57 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126844792</v>
+        <v>126844817</v>
       </c>
       <c r="B6" t="n">
-        <v>98443</v>
+        <v>56849</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>knärot, Lång, Dlr</t>
+          <t>Tjäderspilning, Lång, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478438</v>
+        <v>478451</v>
       </c>
       <c r="R6" t="n">
-        <v>6729346</v>
+        <v>6729364</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1246,13 +1250,17 @@
           <t>15:00</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>spillning, Sandbad</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1271,57 +1279,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126844817</v>
+        <v>126844792</v>
       </c>
       <c r="B7" t="n">
-        <v>56849</v>
+        <v>98443</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tjäderspilning, Lång, Dlr</t>
+          <t>knärot, Lång, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478451</v>
+        <v>478438</v>
       </c>
       <c r="R7" t="n">
-        <v>6729364</v>
+        <v>6729346</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1366,17 +1370,13 @@
           <t>15:00</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>spillning, Sandbad</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 31957-2025 artfynd.xlsx
+++ b/artfynd/A 31957-2025 artfynd.xlsx
@@ -1395,51 +1395,56 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127303713</v>
+        <v>127302956</v>
       </c>
       <c r="B8" t="n">
-        <v>79632</v>
+        <v>56849</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478482</v>
+        <v>478532</v>
       </c>
       <c r="R8" t="n">
-        <v>6729414</v>
+        <v>6729375</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1471,81 +1476,80 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre balningsgrop.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127302956</v>
+        <v>127303713</v>
       </c>
       <c r="B9" t="n">
-        <v>56849</v>
+        <v>79632</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478532</v>
+        <v>478482</v>
       </c>
       <c r="R9" t="n">
-        <v>6729375</v>
+        <v>6729414</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1577,29 +1581,25 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre balningsgrop.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1707,10 +1707,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127302595</v>
+        <v>127303666</v>
       </c>
       <c r="B11" t="n">
-        <v>78773</v>
+        <v>78681</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1718,21 +1718,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1741,17 +1741,17 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478531</v>
+        <v>478520</v>
       </c>
       <c r="R11" t="n">
-        <v>6729399</v>
+        <v>6729405</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1796,22 +1796,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127303666</v>
+        <v>127302595</v>
       </c>
       <c r="B12" t="n">
-        <v>78681</v>
+        <v>78773</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1819,21 +1819,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1842,17 +1842,17 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478520</v>
+        <v>478531</v>
       </c>
       <c r="R12" t="n">
-        <v>6729405</v>
+        <v>6729399</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1897,12 +1897,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 31957-2025 artfynd.xlsx
+++ b/artfynd/A 31957-2025 artfynd.xlsx
@@ -1155,57 +1155,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126844817</v>
+        <v>126844792</v>
       </c>
       <c r="B6" t="n">
-        <v>56849</v>
+        <v>98443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tjäderspilning, Lång, Dlr</t>
+          <t>knärot, Lång, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478451</v>
+        <v>478438</v>
       </c>
       <c r="R6" t="n">
-        <v>6729364</v>
+        <v>6729346</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1250,17 +1246,13 @@
           <t>15:00</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>spillning, Sandbad</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1279,53 +1271,57 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126844792</v>
+        <v>126844817</v>
       </c>
       <c r="B7" t="n">
-        <v>98443</v>
+        <v>56849</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>knärot, Lång, Dlr</t>
+          <t>Tjäderspilning, Lång, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478438</v>
+        <v>478451</v>
       </c>
       <c r="R7" t="n">
-        <v>6729346</v>
+        <v>6729364</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1370,13 +1366,17 @@
           <t>15:00</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>spillning, Sandbad</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1395,56 +1395,51 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127302956</v>
+        <v>127303713</v>
       </c>
       <c r="B8" t="n">
-        <v>56849</v>
+        <v>79632</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478532</v>
+        <v>478482</v>
       </c>
       <c r="R8" t="n">
-        <v>6729375</v>
+        <v>6729414</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1476,80 +1471,81 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Äldre balningsgrop.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127303713</v>
+        <v>127302956</v>
       </c>
       <c r="B9" t="n">
-        <v>79632</v>
+        <v>56849</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478482</v>
+        <v>478532</v>
       </c>
       <c r="R9" t="n">
-        <v>6729414</v>
+        <v>6729375</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1581,25 +1577,29 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre balningsgrop.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 31957-2025 artfynd.xlsx
+++ b/artfynd/A 31957-2025 artfynd.xlsx
@@ -1155,53 +1155,57 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126844792</v>
+        <v>126844817</v>
       </c>
       <c r="B6" t="n">
-        <v>98443</v>
+        <v>56849</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>knärot, Lång, Dlr</t>
+          <t>Tjäderspilning, Lång, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478438</v>
+        <v>478451</v>
       </c>
       <c r="R6" t="n">
-        <v>6729346</v>
+        <v>6729364</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1246,13 +1250,17 @@
           <t>15:00</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>spillning, Sandbad</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1271,57 +1279,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126844817</v>
+        <v>126844792</v>
       </c>
       <c r="B7" t="n">
-        <v>56849</v>
+        <v>98443</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tjäderspilning, Lång, Dlr</t>
+          <t>knärot, Lång, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478451</v>
+        <v>478438</v>
       </c>
       <c r="R7" t="n">
-        <v>6729364</v>
+        <v>6729346</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1366,17 +1370,13 @@
           <t>15:00</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>spillning, Sandbad</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1707,10 +1707,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127303666</v>
+        <v>127302595</v>
       </c>
       <c r="B11" t="n">
-        <v>78681</v>
+        <v>78773</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1718,21 +1718,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1741,17 +1741,17 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478520</v>
+        <v>478531</v>
       </c>
       <c r="R11" t="n">
-        <v>6729405</v>
+        <v>6729399</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1796,22 +1796,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127302595</v>
+        <v>127303666</v>
       </c>
       <c r="B12" t="n">
-        <v>78773</v>
+        <v>78681</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1819,21 +1819,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1842,17 +1842,17 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478531</v>
+        <v>478520</v>
       </c>
       <c r="R12" t="n">
-        <v>6729399</v>
+        <v>6729405</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1897,12 +1897,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 31957-2025 artfynd.xlsx
+++ b/artfynd/A 31957-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126844761</v>
       </c>
       <c r="B2" t="n">
-        <v>56849</v>
+        <v>56853</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>126844749</v>
       </c>
       <c r="B3" t="n">
-        <v>56849</v>
+        <v>56853</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>126844799</v>
       </c>
       <c r="B4" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>126844768</v>
       </c>
       <c r="B5" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>126844817</v>
       </c>
       <c r="B6" t="n">
-        <v>56849</v>
+        <v>56853</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
         <v>126844792</v>
       </c>
       <c r="B7" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1395,51 +1395,56 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127303713</v>
+        <v>127302956</v>
       </c>
       <c r="B8" t="n">
-        <v>79632</v>
+        <v>56853</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478482</v>
+        <v>478532</v>
       </c>
       <c r="R8" t="n">
-        <v>6729414</v>
+        <v>6729375</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1471,81 +1476,80 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre balningsgrop.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127302956</v>
+        <v>127303713</v>
       </c>
       <c r="B9" t="n">
-        <v>56849</v>
+        <v>79636</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478532</v>
+        <v>478482</v>
       </c>
       <c r="R9" t="n">
-        <v>6729375</v>
+        <v>6729414</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1577,29 +1581,25 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre balningsgrop.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1609,7 +1609,7 @@
         <v>127303688</v>
       </c>
       <c r="B10" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>127302595</v>
       </c>
       <c r="B11" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>127303666</v>
       </c>
       <c r="B12" t="n">
-        <v>78681</v>
+        <v>78685</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>127302603</v>
       </c>
       <c r="B13" t="n">
-        <v>56849</v>
+        <v>56853</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>127302681</v>
       </c>
       <c r="B14" t="n">
-        <v>56849</v>
+        <v>56853</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>127302695</v>
       </c>
       <c r="B15" t="n">
-        <v>56849</v>
+        <v>56853</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>127303954</v>
       </c>
       <c r="B16" t="n">
-        <v>56849</v>
+        <v>56853</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>127303837</v>
       </c>
       <c r="B17" t="n">
-        <v>56849</v>
+        <v>56853</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 31957-2025 artfynd.xlsx
+++ b/artfynd/A 31957-2025 artfynd.xlsx
@@ -795,57 +795,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126844749</v>
+        <v>126844799</v>
       </c>
       <c r="B3" t="n">
-        <v>56853</v>
+        <v>98447</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tjäderspilning, Lång, Dlr</t>
+          <t>knärot, Lång, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478451</v>
+        <v>478423</v>
       </c>
       <c r="R3" t="n">
-        <v>6729443</v>
+        <v>6729337</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,17 +886,13 @@
           <t>15:00</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>spillning</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -919,53 +911,57 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126844799</v>
+        <v>126844749</v>
       </c>
       <c r="B4" t="n">
-        <v>98447</v>
+        <v>56853</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>knärot, Lång, Dlr</t>
+          <t>Tjäderspilning, Lång, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478423</v>
+        <v>478451</v>
       </c>
       <c r="R4" t="n">
-        <v>6729337</v>
+        <v>6729443</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,13 +1006,17 @@
           <t>15:00</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>spillning</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1395,56 +1395,51 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127302956</v>
+        <v>127303713</v>
       </c>
       <c r="B8" t="n">
-        <v>56853</v>
+        <v>79636</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478532</v>
+        <v>478482</v>
       </c>
       <c r="R8" t="n">
-        <v>6729375</v>
+        <v>6729414</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1476,80 +1471,81 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Äldre balningsgrop.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127303713</v>
+        <v>127302956</v>
       </c>
       <c r="B9" t="n">
-        <v>79636</v>
+        <v>56853</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478482</v>
+        <v>478532</v>
       </c>
       <c r="R9" t="n">
-        <v>6729414</v>
+        <v>6729375</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1581,25 +1577,29 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre balningsgrop.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1707,10 +1707,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127302595</v>
+        <v>127303666</v>
       </c>
       <c r="B11" t="n">
-        <v>78777</v>
+        <v>78685</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1718,21 +1718,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1741,17 +1741,17 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478531</v>
+        <v>478520</v>
       </c>
       <c r="R11" t="n">
-        <v>6729399</v>
+        <v>6729405</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1796,22 +1796,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127303666</v>
+        <v>127302595</v>
       </c>
       <c r="B12" t="n">
-        <v>78685</v>
+        <v>78777</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1819,21 +1819,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1842,17 +1842,17 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478520</v>
+        <v>478531</v>
       </c>
       <c r="R12" t="n">
-        <v>6729405</v>
+        <v>6729399</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1897,12 +1897,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 31957-2025 artfynd.xlsx
+++ b/artfynd/A 31957-2025 artfynd.xlsx
@@ -1395,51 +1395,56 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127303713</v>
+        <v>127302956</v>
       </c>
       <c r="B8" t="n">
-        <v>79636</v>
+        <v>56853</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478482</v>
+        <v>478532</v>
       </c>
       <c r="R8" t="n">
-        <v>6729414</v>
+        <v>6729375</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1471,81 +1476,80 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre balningsgrop.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127302956</v>
+        <v>127303713</v>
       </c>
       <c r="B9" t="n">
-        <v>56853</v>
+        <v>79636</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478532</v>
+        <v>478482</v>
       </c>
       <c r="R9" t="n">
-        <v>6729375</v>
+        <v>6729414</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1577,29 +1581,25 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre balningsgrop.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 31957-2025 artfynd.xlsx
+++ b/artfynd/A 31957-2025 artfynd.xlsx
@@ -795,53 +795,57 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126844799</v>
+        <v>126844749</v>
       </c>
       <c r="B3" t="n">
-        <v>98447</v>
+        <v>56853</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>knärot, Lång, Dlr</t>
+          <t>Tjäderspilning, Lång, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478423</v>
+        <v>478451</v>
       </c>
       <c r="R3" t="n">
-        <v>6729337</v>
+        <v>6729443</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -886,13 +890,17 @@
           <t>15:00</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>spillning</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -911,57 +919,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126844749</v>
+        <v>126844799</v>
       </c>
       <c r="B4" t="n">
-        <v>56853</v>
+        <v>98447</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tjäderspilning, Lång, Dlr</t>
+          <t>knärot, Lång, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478451</v>
+        <v>478423</v>
       </c>
       <c r="R4" t="n">
-        <v>6729443</v>
+        <v>6729337</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1006,17 +1010,13 @@
           <t>15:00</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>spillning</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 31957-2025 artfynd.xlsx
+++ b/artfynd/A 31957-2025 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>126844799</v>
       </c>
       <c r="B4" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>126844768</v>
       </c>
       <c r="B5" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1155,57 +1155,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126844817</v>
+        <v>126844792</v>
       </c>
       <c r="B6" t="n">
-        <v>56853</v>
+        <v>98448</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tjäderspilning, Lång, Dlr</t>
+          <t>knärot, Lång, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478451</v>
+        <v>478438</v>
       </c>
       <c r="R6" t="n">
-        <v>6729364</v>
+        <v>6729346</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1250,17 +1246,13 @@
           <t>15:00</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>spillning, Sandbad</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1279,53 +1271,57 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126844792</v>
+        <v>126844817</v>
       </c>
       <c r="B7" t="n">
-        <v>98447</v>
+        <v>56853</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>knärot, Lång, Dlr</t>
+          <t>Tjäderspilning, Lång, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478438</v>
+        <v>478451</v>
       </c>
       <c r="R7" t="n">
-        <v>6729346</v>
+        <v>6729364</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1370,13 +1366,17 @@
           <t>15:00</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>spillning, Sandbad</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1395,56 +1395,51 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127302956</v>
+        <v>127303713</v>
       </c>
       <c r="B8" t="n">
-        <v>56853</v>
+        <v>79636</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478532</v>
+        <v>478482</v>
       </c>
       <c r="R8" t="n">
-        <v>6729375</v>
+        <v>6729414</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1476,80 +1471,81 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Äldre balningsgrop.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127303713</v>
+        <v>127302956</v>
       </c>
       <c r="B9" t="n">
-        <v>79636</v>
+        <v>56853</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478482</v>
+        <v>478532</v>
       </c>
       <c r="R9" t="n">
-        <v>6729414</v>
+        <v>6729375</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1581,25 +1577,29 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre balningsgrop.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 31957-2025 artfynd.xlsx
+++ b/artfynd/A 31957-2025 artfynd.xlsx
@@ -1398,7 +1398,7 @@
         <v>127303713</v>
       </c>
       <c r="B8" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>127302956</v>
       </c>
       <c r="B9" t="n">
-        <v>56853</v>
+        <v>56855</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>127303688</v>
       </c>
       <c r="B10" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>127303666</v>
       </c>
       <c r="B11" t="n">
-        <v>78685</v>
+        <v>78687</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>127302595</v>
       </c>
       <c r="B12" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>127302603</v>
       </c>
       <c r="B13" t="n">
-        <v>56853</v>
+        <v>56855</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>127302681</v>
       </c>
       <c r="B14" t="n">
-        <v>56853</v>
+        <v>56855</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>127302695</v>
       </c>
       <c r="B15" t="n">
-        <v>56853</v>
+        <v>56855</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>127303954</v>
       </c>
       <c r="B16" t="n">
-        <v>56853</v>
+        <v>56855</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>127303837</v>
       </c>
       <c r="B17" t="n">
-        <v>56853</v>
+        <v>56855</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 31957-2025 artfynd.xlsx
+++ b/artfynd/A 31957-2025 artfynd.xlsx
@@ -1395,51 +1395,56 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127303713</v>
+        <v>127302956</v>
       </c>
       <c r="B8" t="n">
-        <v>79638</v>
+        <v>56855</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478482</v>
+        <v>478532</v>
       </c>
       <c r="R8" t="n">
-        <v>6729414</v>
+        <v>6729375</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1471,81 +1476,80 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre balningsgrop.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127302956</v>
+        <v>127303713</v>
       </c>
       <c r="B9" t="n">
-        <v>56855</v>
+        <v>79638</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478532</v>
+        <v>478482</v>
       </c>
       <c r="R9" t="n">
-        <v>6729375</v>
+        <v>6729414</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1577,29 +1581,25 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre balningsgrop.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 31957-2025 artfynd.xlsx
+++ b/artfynd/A 31957-2025 artfynd.xlsx
@@ -1395,56 +1395,51 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127302956</v>
+        <v>127303713</v>
       </c>
       <c r="B8" t="n">
-        <v>56855</v>
+        <v>79638</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478532</v>
+        <v>478482</v>
       </c>
       <c r="R8" t="n">
-        <v>6729375</v>
+        <v>6729414</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1476,80 +1471,81 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Äldre balningsgrop.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127303713</v>
+        <v>127302956</v>
       </c>
       <c r="B9" t="n">
-        <v>79638</v>
+        <v>56855</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478482</v>
+        <v>478532</v>
       </c>
       <c r="R9" t="n">
-        <v>6729414</v>
+        <v>6729375</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1581,25 +1577,29 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre balningsgrop.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 31957-2025 artfynd.xlsx
+++ b/artfynd/A 31957-2025 artfynd.xlsx
@@ -1398,7 +1398,7 @@
         <v>127303713</v>
       </c>
       <c r="B8" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>127302956</v>
       </c>
       <c r="B9" t="n">
-        <v>56855</v>
+        <v>56858</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>127303688</v>
       </c>
       <c r="B10" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>127303666</v>
       </c>
       <c r="B11" t="n">
-        <v>78687</v>
+        <v>78690</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>127302595</v>
       </c>
       <c r="B12" t="n">
-        <v>78779</v>
+        <v>78782</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>127302603</v>
       </c>
       <c r="B13" t="n">
-        <v>56855</v>
+        <v>56858</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>127302681</v>
       </c>
       <c r="B14" t="n">
-        <v>56855</v>
+        <v>56858</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>127302695</v>
       </c>
       <c r="B15" t="n">
-        <v>56855</v>
+        <v>56858</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>127303954</v>
       </c>
       <c r="B16" t="n">
-        <v>56855</v>
+        <v>56858</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>127303837</v>
       </c>
       <c r="B17" t="n">
-        <v>56855</v>
+        <v>56858</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 31957-2025 artfynd.xlsx
+++ b/artfynd/A 31957-2025 artfynd.xlsx
@@ -1395,51 +1395,56 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127303713</v>
+        <v>127302956</v>
       </c>
       <c r="B8" t="n">
-        <v>79641</v>
+        <v>56864</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478482</v>
+        <v>478532</v>
       </c>
       <c r="R8" t="n">
-        <v>6729414</v>
+        <v>6729375</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1471,81 +1476,80 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre balningsgrop.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127302956</v>
+        <v>127303713</v>
       </c>
       <c r="B9" t="n">
-        <v>56858</v>
+        <v>79647</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478532</v>
+        <v>478482</v>
       </c>
       <c r="R9" t="n">
-        <v>6729375</v>
+        <v>6729414</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1577,29 +1581,25 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre balningsgrop.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1609,7 +1609,7 @@
         <v>127303688</v>
       </c>
       <c r="B10" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>127303666</v>
       </c>
       <c r="B11" t="n">
-        <v>78690</v>
+        <v>78696</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>127302595</v>
       </c>
       <c r="B12" t="n">
-        <v>78782</v>
+        <v>78788</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>127302603</v>
       </c>
       <c r="B13" t="n">
-        <v>56858</v>
+        <v>56864</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>127302681</v>
       </c>
       <c r="B14" t="n">
-        <v>56858</v>
+        <v>56864</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>127302695</v>
       </c>
       <c r="B15" t="n">
-        <v>56858</v>
+        <v>56864</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>127303954</v>
       </c>
       <c r="B16" t="n">
-        <v>56858</v>
+        <v>56864</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>127303837</v>
       </c>
       <c r="B17" t="n">
-        <v>56858</v>
+        <v>56864</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 31957-2025 artfynd.xlsx
+++ b/artfynd/A 31957-2025 artfynd.xlsx
@@ -1707,10 +1707,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127303666</v>
+        <v>127302595</v>
       </c>
       <c r="B11" t="n">
-        <v>78696</v>
+        <v>78788</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1718,21 +1718,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1741,17 +1741,17 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478520</v>
+        <v>478531</v>
       </c>
       <c r="R11" t="n">
-        <v>6729405</v>
+        <v>6729399</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1796,22 +1796,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127302595</v>
+        <v>127303666</v>
       </c>
       <c r="B12" t="n">
-        <v>78788</v>
+        <v>78696</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1819,21 +1819,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1842,17 +1842,17 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478531</v>
+        <v>478520</v>
       </c>
       <c r="R12" t="n">
-        <v>6729399</v>
+        <v>6729405</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1897,12 +1897,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 31957-2025 artfynd.xlsx
+++ b/artfynd/A 31957-2025 artfynd.xlsx
@@ -1707,10 +1707,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127302595</v>
+        <v>127303666</v>
       </c>
       <c r="B11" t="n">
-        <v>78788</v>
+        <v>78696</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1718,21 +1718,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1741,17 +1741,17 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478531</v>
+        <v>478520</v>
       </c>
       <c r="R11" t="n">
-        <v>6729399</v>
+        <v>6729405</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1796,22 +1796,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127303666</v>
+        <v>127302595</v>
       </c>
       <c r="B12" t="n">
-        <v>78696</v>
+        <v>78788</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1819,21 +1819,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1842,17 +1842,17 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478520</v>
+        <v>478531</v>
       </c>
       <c r="R12" t="n">
-        <v>6729405</v>
+        <v>6729399</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1897,12 +1897,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 31957-2025 artfynd.xlsx
+++ b/artfynd/A 31957-2025 artfynd.xlsx
@@ -1395,56 +1395,51 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127302956</v>
+        <v>127303713</v>
       </c>
       <c r="B8" t="n">
-        <v>56864</v>
+        <v>79647</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478532</v>
+        <v>478482</v>
       </c>
       <c r="R8" t="n">
-        <v>6729375</v>
+        <v>6729414</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1476,80 +1471,81 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Äldre balningsgrop.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127303713</v>
+        <v>127302956</v>
       </c>
       <c r="B9" t="n">
-        <v>79647</v>
+        <v>56864</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478482</v>
+        <v>478532</v>
       </c>
       <c r="R9" t="n">
-        <v>6729414</v>
+        <v>6729375</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1581,25 +1577,29 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre balningsgrop.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 31957-2025 artfynd.xlsx
+++ b/artfynd/A 31957-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126844761</v>
       </c>
       <c r="B2" t="n">
-        <v>56853</v>
+        <v>56849</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>126844749</v>
       </c>
       <c r="B3" t="n">
-        <v>56853</v>
+        <v>56849</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>126844799</v>
       </c>
       <c r="B4" t="n">
-        <v>98448</v>
+        <v>98436</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>126844768</v>
       </c>
       <c r="B5" t="n">
-        <v>98448</v>
+        <v>98436</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1155,53 +1155,57 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126844792</v>
+        <v>126844817</v>
       </c>
       <c r="B6" t="n">
-        <v>98448</v>
+        <v>56849</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>knärot, Lång, Dlr</t>
+          <t>Tjäderspilning, Lång, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478438</v>
+        <v>478451</v>
       </c>
       <c r="R6" t="n">
-        <v>6729346</v>
+        <v>6729364</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1246,13 +1250,17 @@
           <t>15:00</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>spillning, Sandbad</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1271,57 +1279,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126844817</v>
+        <v>126844792</v>
       </c>
       <c r="B7" t="n">
-        <v>56853</v>
+        <v>98436</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tjäderspilning, Lång, Dlr</t>
+          <t>knärot, Lång, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478451</v>
+        <v>478438</v>
       </c>
       <c r="R7" t="n">
-        <v>6729364</v>
+        <v>6729346</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1366,17 +1370,13 @@
           <t>15:00</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>spillning, Sandbad</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1395,51 +1395,56 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127303713</v>
+        <v>127302956</v>
       </c>
       <c r="B8" t="n">
-        <v>79647</v>
+        <v>56849</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478482</v>
+        <v>478532</v>
       </c>
       <c r="R8" t="n">
-        <v>6729414</v>
+        <v>6729375</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1471,81 +1476,80 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre balningsgrop.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127302956</v>
+        <v>127303713</v>
       </c>
       <c r="B9" t="n">
-        <v>56864</v>
+        <v>79629</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478532</v>
+        <v>478482</v>
       </c>
       <c r="R9" t="n">
-        <v>6729375</v>
+        <v>6729414</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1577,29 +1581,25 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre balningsgrop.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1609,7 +1609,7 @@
         <v>127303688</v>
       </c>
       <c r="B10" t="n">
-        <v>79647</v>
+        <v>79629</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>127303666</v>
       </c>
       <c r="B11" t="n">
-        <v>78696</v>
+        <v>78678</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>127302595</v>
       </c>
       <c r="B12" t="n">
-        <v>78788</v>
+        <v>78770</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 31957-2025 artfynd.xlsx
+++ b/artfynd/A 31957-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,56 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126844761</v>
+        <v>127303666</v>
       </c>
       <c r="B2" t="n">
-        <v>56853</v>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tjäderspilning, Lång, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478522</v>
+        <v>478520</v>
       </c>
       <c r="R2" t="n">
-        <v>6729467</v>
+        <v>6729405</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,27 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>spillning</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,75 +757,67 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126844749</v>
+        <v>127303033</v>
       </c>
       <c r="B3" t="n">
-        <v>56853</v>
+        <v>79946</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tjäderspilning, Lång, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478451</v>
+        <v>478430</v>
       </c>
       <c r="R3" t="n">
-        <v>6729443</v>
+        <v>6729394</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,27 +844,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>spillning</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,74 +858,70 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126844799</v>
+        <v>127303688</v>
       </c>
       <c r="B4" t="n">
-        <v>98448</v>
+        <v>79946</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>knärot, Lång, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478423</v>
+        <v>478523</v>
       </c>
       <c r="R4" t="n">
-        <v>6729337</v>
+        <v>6729413</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,22 +945,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,72 +966,63 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126844768</v>
+        <v>127303713</v>
       </c>
       <c r="B5" t="n">
-        <v>98448</v>
+        <v>79946</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>knärot, Lång, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478550</v>
+        <v>478482</v>
       </c>
       <c r="R5" t="n">
-        <v>6729448</v>
+        <v>6729414</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1112,22 +1046,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,68 +1067,68 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126844792</v>
+        <v>126844716</v>
       </c>
       <c r="B6" t="n">
-        <v>98448</v>
+        <v>57141</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>knärot, Lång, Dlr</t>
+          <t>Tjäder, Lång, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478438</v>
+        <v>478441</v>
       </c>
       <c r="R6" t="n">
-        <v>6729346</v>
+        <v>6729469</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1252,7 +1176,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1271,10 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126844817</v>
+        <v>126844749</v>
       </c>
       <c r="B7" t="n">
-        <v>56853</v>
+        <v>57141</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1321,7 +1244,7 @@
         <v>478451</v>
       </c>
       <c r="R7" t="n">
-        <v>6729364</v>
+        <v>6729443</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1368,7 +1291,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>spillning, Sandbad</t>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1395,51 +1318,56 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127303713</v>
+        <v>126844761</v>
       </c>
       <c r="B8" t="n">
-        <v>79647</v>
+        <v>57141</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>Tjäderspilning, Lång, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478482</v>
+        <v>478522</v>
       </c>
       <c r="R8" t="n">
-        <v>6729414</v>
+        <v>6729467</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1463,12 +1391,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1477,29 +1420,28 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127302956</v>
+        <v>126844817</v>
       </c>
       <c r="B9" t="n">
-        <v>56864</v>
+        <v>57141</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1524,25 +1466,29 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Tjäderspilning, Lång, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478532</v>
+        <v>478451</v>
       </c>
       <c r="R9" t="n">
-        <v>6729375</v>
+        <v>6729364</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1569,17 +1515,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Äldre balningsgrop.</t>
+          <t>spillning, Sandbad</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1594,49 +1550,54 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127303688</v>
+        <v>127302603</v>
       </c>
       <c r="B10" t="n">
-        <v>79647</v>
+        <v>57141</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1644,13 +1605,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478523</v>
+        <v>478336</v>
       </c>
       <c r="R10" t="n">
-        <v>6729413</v>
+        <v>6729407</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1677,67 +1638,81 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127303666</v>
+        <v>127302681</v>
       </c>
       <c r="B11" t="n">
-        <v>78696</v>
+        <v>57141</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1745,13 +1720,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478520</v>
+        <v>478358</v>
       </c>
       <c r="R11" t="n">
-        <v>6729405</v>
+        <v>6729449</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1778,78 +1753,97 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>på liten sten</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127302595</v>
+        <v>127302695</v>
       </c>
       <c r="B12" t="n">
-        <v>78788</v>
+        <v>57141</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>N Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478531</v>
+        <v>478360</v>
       </c>
       <c r="R12" t="n">
-        <v>6729399</v>
+        <v>6729494</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1879,40 +1873,49 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127302603</v>
+        <v>127302956</v>
       </c>
       <c r="B13" t="n">
-        <v>56864</v>
+        <v>57141</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1942,20 +1945,20 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>N Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478336</v>
+        <v>478532</v>
       </c>
       <c r="R13" t="n">
-        <v>6729407</v>
+        <v>6729375</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1985,19 +1988,14 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre balningsgrop.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2012,22 +2010,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127302681</v>
+        <v>127303805</v>
       </c>
       <c r="B14" t="n">
-        <v>56864</v>
+        <v>57141</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2057,7 +2055,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2067,10 +2065,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478358</v>
+        <v>478365</v>
       </c>
       <c r="R14" t="n">
-        <v>6729449</v>
+        <v>6729523</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2113,11 +2111,6 @@
       <c r="AB14" t="inlineStr">
         <is>
           <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>på liten sten</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2144,10 +2137,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127302695</v>
+        <v>127303837</v>
       </c>
       <c r="B15" t="n">
-        <v>56864</v>
+        <v>57141</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2177,7 +2170,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2187,10 +2180,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478360</v>
+        <v>478296</v>
       </c>
       <c r="R15" t="n">
-        <v>6729494</v>
+        <v>6729357</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2262,7 +2255,7 @@
         <v>127303954</v>
       </c>
       <c r="B16" t="n">
-        <v>56864</v>
+        <v>57141</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2374,10 +2367,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127303837</v>
+        <v>127303990</v>
       </c>
       <c r="B17" t="n">
-        <v>56864</v>
+        <v>57141</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2407,7 +2400,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2417,10 +2410,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478296</v>
+        <v>478299</v>
       </c>
       <c r="R17" t="n">
-        <v>6729357</v>
+        <v>6729464</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2486,6 +2479,579 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>127304031</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>478342</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6729512</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>sandbad</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>126844768</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>knärot, Lång, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>478550</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6729448</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>126844792</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>knärot, Lång, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>478438</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6729346</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>126844799</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>knärot, Lång, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>478423</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6729337</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>127302595</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>N Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>478531</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6729399</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31957-2025 artfynd.xlsx
+++ b/artfynd/A 31957-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127303666</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127303033</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127303688</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127303713</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1191,6 +1216,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126844716</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1315,6 +1345,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126844749</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1435,6 +1470,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126844761</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1559,6 +1599,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126844817</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1674,6 +1719,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127302603</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1794,6 +1844,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127302681</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1909,6 +1964,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127302695</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2019,6 +2079,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127302956</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2134,6 +2199,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127303805</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2249,6 +2319,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127303837</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2364,6 +2439,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127303954</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2479,6 +2559,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127303990</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2599,6 +2684,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127304031</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2719,6 +2809,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126844768</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2835,6 +2930,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126844792</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2951,6 +3051,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126844799</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3052,8 +3157,36 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127302595</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>